--- a/output/yearly_benthic_cover_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_19_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59368732771628</v>
+        <v>45.40771257441885</v>
       </c>
       <c r="M2" t="n">
-        <v>99.56731072803132</v>
+        <v>99.68681833970987</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09341448150859</v>
+        <v>87.96595417706625</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94096712336812</v>
+        <v>45.92470992680119</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228890766899731</v>
+        <v>2.228576142588665</v>
       </c>
       <c r="E3" t="n">
-        <v>5.717046882310288</v>
+        <v>5.700624252823604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429635889665771</v>
+        <v>0.7428587141962218</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97668103003978</v>
+        <v>33.972404597964</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17632509246254</v>
+        <v>34.1715008530262</v>
       </c>
       <c r="I3" t="n">
-        <v>6.607984689788571</v>
+        <v>6.507122652741154</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643522431041107</v>
+        <v>4.642866963726386</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90658551849139</v>
+        <v>12.03404582293376</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91527163691015</v>
+        <v>48.80765572606296</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7628242787697</v>
+        <v>106.7664114757979</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27994193255211</v>
+        <v>86.9551715950835</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76988537061938</v>
+        <v>42.53744816069266</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190247274314319</v>
+        <v>2.179346924126636</v>
       </c>
       <c r="E4" t="n">
-        <v>6.537637186499904</v>
+        <v>6.480347141780478</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445293804232268</v>
+        <v>0.7444061085358175</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38760881485557</v>
+        <v>33.22195461527194</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24835149946843</v>
+        <v>34.2426809926476</v>
       </c>
       <c r="I4" t="n">
-        <v>5.518259149345492</v>
+        <v>5.433897634372154</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653308627645167</v>
+        <v>4.652538178348859</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72005806744791</v>
+        <v>13.04482840491653</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32650143166079</v>
+        <v>44.23697002737021</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81644486972807</v>
+        <v>99.8192465929794</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22797209555242</v>
+        <v>85.60719402766539</v>
       </c>
       <c r="C5" t="n">
-        <v>42.57447770094686</v>
+        <v>42.0327852270707</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139341853699691</v>
+        <v>2.112929266247751</v>
       </c>
       <c r="E5" t="n">
-        <v>7.153480097524096</v>
+        <v>7.038893483566132</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458552657944677</v>
+        <v>0.7457209549817141</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61161868352715</v>
+        <v>32.20948414015965</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30934222654551</v>
+        <v>34.30316392915885</v>
       </c>
       <c r="I5" t="n">
-        <v>4.606738557246056</v>
+        <v>4.53624628491558</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661595411215423</v>
+        <v>4.660755968635713</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77202790444761</v>
+        <v>14.39280597233462</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50020941823484</v>
+        <v>43.42346719963992</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84671502362932</v>
+        <v>99.84905839904523</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.00175690575017</v>
+        <v>84.06408670538505</v>
       </c>
       <c r="C6" t="n">
-        <v>42.06390551036071</v>
+        <v>41.19395472891318</v>
       </c>
       <c r="D6" t="n">
-        <v>2.079871171314116</v>
+        <v>2.037153684042849</v>
       </c>
       <c r="E6" t="n">
-        <v>7.595412921928005</v>
+        <v>7.417438985388335</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469797983151429</v>
+        <v>0.7468404223574454</v>
       </c>
       <c r="G6" t="n">
-        <v>31.70506173777603</v>
+        <v>31.05436150911461</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36107072249657</v>
+        <v>34.35465942844249</v>
       </c>
       <c r="I6" t="n">
-        <v>3.844736814450665</v>
+        <v>3.78588003630529</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668623739469643</v>
+        <v>4.667752639734034</v>
       </c>
       <c r="K6" t="n">
-        <v>14.99824309424981</v>
+        <v>15.93591329461495</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80988643546598</v>
+        <v>42.74412513522421</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87203504007651</v>
+        <v>99.87399315875234</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.57898333086492</v>
+        <v>82.27237169703074</v>
       </c>
       <c r="C7" t="n">
-        <v>41.23854327867729</v>
+        <v>39.989896264258</v>
       </c>
       <c r="D7" t="n">
-        <v>2.010928894902231</v>
+        <v>1.949542148058497</v>
       </c>
       <c r="E7" t="n">
-        <v>7.87831933464511</v>
+        <v>7.624928046246666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479355194492329</v>
+        <v>0.7477962809122313</v>
       </c>
       <c r="G7" t="n">
-        <v>30.65412206414204</v>
+        <v>29.7188116524011</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4050338946647</v>
+        <v>34.39862892196264</v>
       </c>
       <c r="I7" t="n">
-        <v>3.208046626503897</v>
+        <v>3.158937891748157</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674596996557705</v>
+        <v>4.673726755701446</v>
       </c>
       <c r="K7" t="n">
-        <v>16.42101666913508</v>
+        <v>17.72762830296926</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23364180734177</v>
+        <v>42.17731209843093</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89320175515414</v>
+        <v>99.8948366656582</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.51607661071027</v>
+        <v>87.23328372624171</v>
       </c>
       <c r="C8" t="n">
-        <v>43.5752297970222</v>
+        <v>42.36585042004985</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015233459565461</v>
+        <v>1.953728923317374</v>
       </c>
       <c r="E8" t="n">
-        <v>9.736852502052972</v>
+        <v>9.506712118338111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495365391648264</v>
+        <v>0.7494022246312328</v>
       </c>
       <c r="G8" t="n">
-        <v>31.16688378893437</v>
+        <v>30.24699071856401</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47868080158201</v>
+        <v>34.47250233303672</v>
       </c>
       <c r="I8" t="n">
-        <v>5.684286149630479</v>
+        <v>5.620183504409051</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684603369780165</v>
+        <v>4.683763903945206</v>
       </c>
       <c r="K8" t="n">
-        <v>11.48392338928973</v>
+        <v>12.76671627375829</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7517753323182</v>
+        <v>44.68049531817483</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81092851863013</v>
+        <v>99.81306201198298</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.66215714736271</v>
+        <v>84.89641367435718</v>
       </c>
       <c r="C9" t="n">
-        <v>42.60407101381875</v>
+        <v>40.90054497524526</v>
       </c>
       <c r="D9" t="n">
-        <v>1.931703354865256</v>
+        <v>1.847659031993298</v>
       </c>
       <c r="E9" t="n">
-        <v>10.12419159272534</v>
+        <v>9.772602337203621</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509046735051834</v>
+        <v>0.7507828409072713</v>
       </c>
       <c r="G9" t="n">
-        <v>29.87503690453906</v>
+        <v>28.60485143296095</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54161498123843</v>
+        <v>34.53601068173448</v>
       </c>
       <c r="I9" t="n">
-        <v>4.745551431082045</v>
+        <v>4.692114593887113</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693154209407396</v>
+        <v>4.692392755670446</v>
       </c>
       <c r="K9" t="n">
-        <v>13.33784285263729</v>
+        <v>15.1035863256428</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90018929605424</v>
+        <v>43.83975249065613</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84210316251028</v>
+        <v>99.8438837915442</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.73644487556399</v>
+        <v>82.41817237761958</v>
       </c>
       <c r="C10" t="n">
-        <v>41.41522861926415</v>
+        <v>39.14933692881186</v>
       </c>
       <c r="D10" t="n">
-        <v>1.845859826925833</v>
+        <v>1.736572264901908</v>
       </c>
       <c r="E10" t="n">
-        <v>10.33441099769995</v>
+        <v>9.837759150964773</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520746439510378</v>
+        <v>0.7519720132692064</v>
       </c>
       <c r="G10" t="n">
-        <v>28.5474114393004</v>
+        <v>26.88504252136267</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59543362174774</v>
+        <v>34.59071261038349</v>
       </c>
       <c r="I10" t="n">
-        <v>3.96078782124503</v>
+        <v>3.916288733805008</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700466524693987</v>
+        <v>4.69982508293254</v>
       </c>
       <c r="K10" t="n">
-        <v>15.26355512443604</v>
+        <v>17.58182762238041</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1893953832142</v>
+        <v>43.13849893231085</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86817912691438</v>
+        <v>99.86966348350312</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.61920621062625</v>
+        <v>79.83619914181045</v>
       </c>
       <c r="C11" t="n">
-        <v>39.91262766255684</v>
+        <v>37.17330170549567</v>
       </c>
       <c r="D11" t="n">
-        <v>1.752235753499498</v>
+        <v>1.622197769780137</v>
       </c>
       <c r="E11" t="n">
-        <v>10.36108108486088</v>
+        <v>9.734493713420937</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530774979951518</v>
+        <v>0.7529980577905031</v>
       </c>
       <c r="G11" t="n">
-        <v>27.09945482540295</v>
+        <v>25.1143340821824</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64156490777698</v>
+        <v>34.63791065836314</v>
       </c>
       <c r="I11" t="n">
-        <v>3.305057778621089</v>
+        <v>3.268026999082689</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706734362469699</v>
+        <v>4.706237861190644</v>
       </c>
       <c r="K11" t="n">
-        <v>17.38079378937378</v>
+        <v>20.16380085818956</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59655666414591</v>
+        <v>42.55411163815354</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88997811607652</v>
+        <v>99.89121420183876</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.3909716498401</v>
+        <v>77.31987926933931</v>
       </c>
       <c r="C12" t="n">
-        <v>38.19665040355861</v>
+        <v>35.16159638946431</v>
       </c>
       <c r="D12" t="n">
-        <v>1.654555867106189</v>
+        <v>1.512049413139449</v>
       </c>
       <c r="E12" t="n">
-        <v>10.24305434933326</v>
+        <v>9.527940985337841</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539385020564026</v>
+        <v>0.7538831652749899</v>
       </c>
       <c r="G12" t="n">
-        <v>25.58877245096826</v>
+        <v>23.40905333355176</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68117109459452</v>
+        <v>34.67862560264953</v>
       </c>
       <c r="I12" t="n">
-        <v>2.757363747928954</v>
+        <v>2.726556986417034</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712115637852516</v>
+        <v>4.711769782968687</v>
       </c>
       <c r="K12" t="n">
-        <v>19.6090283501599</v>
+        <v>22.68012073066071</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10251408576425</v>
+        <v>42.06750435212269</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90819283948277</v>
+        <v>99.90922147224769</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.20529877451578</v>
+        <v>74.7457294513617</v>
       </c>
       <c r="C13" t="n">
-        <v>36.43761548135218</v>
+        <v>33.00746554966217</v>
       </c>
       <c r="D13" t="n">
-        <v>1.559613161083219</v>
+        <v>1.400483002795759</v>
       </c>
       <c r="E13" t="n">
-        <v>10.03862395878221</v>
+        <v>9.20399541390651</v>
       </c>
       <c r="F13" t="n">
-        <v>0.75467762529214</v>
+        <v>0.7546478281762466</v>
       </c>
       <c r="G13" t="n">
-        <v>24.12042233442003</v>
+        <v>21.68181874235821</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71517076343844</v>
+        <v>34.71380009610734</v>
       </c>
       <c r="I13" t="n">
-        <v>2.300055773423881</v>
+        <v>2.27443544191609</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716735158075875</v>
+        <v>4.716548926101542</v>
       </c>
       <c r="K13" t="n">
-        <v>21.7947012254842</v>
+        <v>25.25427054863829</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69108985572116</v>
+        <v>41.66252620763242</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92340656255755</v>
+        <v>99.92426230593287</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.44310806878053</v>
+        <v>82.36339336705819</v>
       </c>
       <c r="C14" t="n">
-        <v>40.29224035061991</v>
+        <v>37.85022715582362</v>
       </c>
       <c r="D14" t="n">
-        <v>1.561435989214729</v>
+        <v>1.402082684823556</v>
       </c>
       <c r="E14" t="n">
-        <v>12.20877644032463</v>
+        <v>11.85709237147576</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555596694040579</v>
+        <v>0.7555098140522908</v>
       </c>
       <c r="G14" t="n">
-        <v>25.81356058907486</v>
+        <v>23.8787761755002</v>
       </c>
       <c r="H14" t="n">
-        <v>36.42069183581024</v>
+        <v>36.92564312680143</v>
       </c>
       <c r="I14" t="n">
-        <v>2.960835611176662</v>
+        <v>2.822352856578129</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722247933775362</v>
+        <v>4.721936337826818</v>
       </c>
       <c r="K14" t="n">
-        <v>15.55689193121947</v>
+        <v>17.63660663294182</v>
       </c>
       <c r="L14" t="n">
-        <v>44.05228841426148</v>
+        <v>44.41919511984044</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90142069610086</v>
+        <v>99.90602890860588</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.81911904543831</v>
+        <v>81.60474782860148</v>
       </c>
       <c r="C15" t="n">
-        <v>40.12657083289502</v>
+        <v>37.50152895631324</v>
       </c>
       <c r="D15" t="n">
-        <v>1.538331339470066</v>
+        <v>1.371896043543016</v>
       </c>
       <c r="E15" t="n">
-        <v>12.43975360978729</v>
+        <v>12.01948557592695</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563017717775236</v>
+        <v>0.7562363396563185</v>
       </c>
       <c r="G15" t="n">
-        <v>25.43159598713614</v>
+        <v>23.38997382584939</v>
       </c>
       <c r="H15" t="n">
-        <v>36.45646383761115</v>
+        <v>36.98645647634121</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46978642604662</v>
+        <v>2.354222444432595</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726886073609522</v>
+        <v>4.726477122851991</v>
       </c>
       <c r="K15" t="n">
-        <v>16.1808809545617</v>
+        <v>18.39525217139855</v>
       </c>
       <c r="L15" t="n">
-        <v>43.61030277889949</v>
+        <v>44.02482018182771</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91775456635621</v>
+        <v>99.92160130953951</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.57653239958138</v>
+        <v>79.05208598783526</v>
       </c>
       <c r="C16" t="n">
-        <v>38.26642195482059</v>
+        <v>35.31190528371398</v>
       </c>
       <c r="D16" t="n">
-        <v>1.452014556037368</v>
+        <v>1.27774212356282</v>
       </c>
       <c r="E16" t="n">
-        <v>12.08506546859722</v>
+        <v>11.52182824669021</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569383505720364</v>
+        <v>0.7568624467410054</v>
       </c>
       <c r="G16" t="n">
-        <v>24.00461240639097</v>
+        <v>21.78470808118668</v>
       </c>
       <c r="H16" t="n">
-        <v>36.48714922361441</v>
+        <v>37.01707849385471</v>
       </c>
       <c r="I16" t="n">
-        <v>2.059887703294165</v>
+        <v>1.963476303668525</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730864691075228</v>
+        <v>4.730390292131283</v>
       </c>
       <c r="K16" t="n">
-        <v>18.4234676004186</v>
+        <v>20.94791401216477</v>
       </c>
       <c r="L16" t="n">
-        <v>43.24150526625952</v>
+        <v>43.67478563622036</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93139482149871</v>
+        <v>99.93460493209912</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.11282029457202</v>
+        <v>81.1505717056628</v>
       </c>
       <c r="C17" t="n">
-        <v>39.39891421076848</v>
+        <v>36.82788469619786</v>
       </c>
       <c r="D17" t="n">
-        <v>1.453208275083378</v>
+        <v>1.278754961419156</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8164149250431</v>
+        <v>12.43573814606815</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575606389106598</v>
+        <v>0.7574623948243957</v>
       </c>
       <c r="G17" t="n">
-        <v>24.40412070424556</v>
+        <v>22.38512184168357</v>
       </c>
       <c r="H17" t="n">
-        <v>36.89691956869111</v>
+        <v>37.62956661670624</v>
       </c>
       <c r="I17" t="n">
-        <v>2.049842189406584</v>
+        <v>1.929787777308822</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734753993191624</v>
+        <v>4.734139967652473</v>
       </c>
       <c r="K17" t="n">
-        <v>16.88717970542798</v>
+        <v>18.84942829433721</v>
       </c>
       <c r="L17" t="n">
-        <v>43.64563413803059</v>
+        <v>44.2584116998344</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93172805422707</v>
+        <v>99.93572469036945</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.83677568695438</v>
+        <v>78.6133134863762</v>
       </c>
       <c r="C18" t="n">
-        <v>37.4399602397493</v>
+        <v>34.58784520489046</v>
       </c>
       <c r="D18" t="n">
-        <v>1.368647458852345</v>
+        <v>1.189689013667712</v>
       </c>
       <c r="E18" t="n">
-        <v>12.35554083572245</v>
+        <v>11.83779148795236</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758094627975105</v>
+        <v>0.7579792492808078</v>
       </c>
       <c r="G18" t="n">
-        <v>22.98406798259886</v>
+        <v>20.82598646976804</v>
       </c>
       <c r="H18" t="n">
-        <v>36.92292745578214</v>
+        <v>37.65524315105513</v>
       </c>
       <c r="I18" t="n">
-        <v>1.709405901179088</v>
+        <v>1.609253806647094</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738091424844406</v>
+        <v>4.737370308005048</v>
       </c>
       <c r="K18" t="n">
-        <v>19.16322431304562</v>
+        <v>21.38668651362379</v>
       </c>
       <c r="L18" t="n">
-        <v>43.33987538638822</v>
+        <v>43.9718630654494</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94305993918314</v>
+        <v>99.94639478396365</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.88047488320166</v>
+        <v>77.6494532253008</v>
       </c>
       <c r="C19" t="n">
-        <v>36.7474675876709</v>
+        <v>33.86442327521165</v>
       </c>
       <c r="D19" t="n">
-        <v>1.333785145544594</v>
+        <v>1.156213342703192</v>
       </c>
       <c r="E19" t="n">
-        <v>12.27837806770927</v>
+        <v>11.72941099747144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585455315872776</v>
+        <v>0.7584179594193252</v>
       </c>
       <c r="G19" t="n">
-        <v>22.39861569982627</v>
+        <v>20.23998133517895</v>
       </c>
       <c r="H19" t="n">
-        <v>36.94488867374548</v>
+        <v>37.67703759589565</v>
       </c>
       <c r="I19" t="n">
-        <v>1.425352192368283</v>
+        <v>1.348279748261442</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740909572420485</v>
+        <v>4.740112246370782</v>
       </c>
       <c r="K19" t="n">
-        <v>20.11952511679835</v>
+        <v>22.35054677469923</v>
       </c>
       <c r="L19" t="n">
-        <v>43.08552379827578</v>
+        <v>43.74011328908818</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95251650274503</v>
+        <v>99.95508333899905</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.44117544984481</v>
+        <v>74.96265519570332</v>
       </c>
       <c r="C20" t="n">
-        <v>34.52799059358396</v>
+        <v>31.38448668132288</v>
       </c>
       <c r="D20" t="n">
-        <v>1.244073213089772</v>
+        <v>1.06296464071437</v>
       </c>
       <c r="E20" t="n">
-        <v>11.65058699664332</v>
+        <v>10.97078770837981</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589335492564634</v>
+        <v>0.7587970632658304</v>
       </c>
       <c r="G20" t="n">
-        <v>20.89205888634199</v>
+        <v>18.6076251617319</v>
       </c>
       <c r="H20" t="n">
-        <v>36.96378703777845</v>
+        <v>37.69587089183771</v>
       </c>
       <c r="I20" t="n">
-        <v>1.188401083881935</v>
+        <v>1.124128084362259</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743334682852896</v>
+        <v>4.74248164541144</v>
       </c>
       <c r="K20" t="n">
-        <v>22.55882455015519</v>
+        <v>25.03734480429668</v>
       </c>
       <c r="L20" t="n">
-        <v>42.8735917398062</v>
+        <v>43.54071629915097</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96040688354535</v>
+        <v>99.96254778477052</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.83690991977049</v>
+        <v>81.38492470014353</v>
       </c>
       <c r="C21" t="n">
-        <v>37.83724944917147</v>
+        <v>35.45282984229915</v>
       </c>
       <c r="D21" t="n">
-        <v>1.244941584167688</v>
+        <v>1.063637551821851</v>
       </c>
       <c r="E21" t="n">
-        <v>13.45021809619156</v>
+        <v>13.13414525602011</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594632897390174</v>
+        <v>0.759277420704486</v>
       </c>
       <c r="G21" t="n">
-        <v>22.40903712174588</v>
+        <v>20.518213072433</v>
       </c>
       <c r="H21" t="n">
-        <v>38.49198344246048</v>
+        <v>39.61854264059149</v>
       </c>
       <c r="I21" t="n">
-        <v>1.734620824597011</v>
+        <v>1.545624879169558</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746645560868859</v>
+        <v>4.745483879403037</v>
       </c>
       <c r="K21" t="n">
-        <v>17.1630900802295</v>
+        <v>18.61507529985645</v>
       </c>
       <c r="L21" t="n">
-        <v>44.94188010750964</v>
+        <v>45.88060662323066</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94221963691061</v>
+        <v>99.94851176538627</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_19_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.40771257441885</v>
+        <v>45.72753214021292</v>
       </c>
       <c r="M2" t="n">
-        <v>99.68681833970987</v>
+        <v>99.28854918372429</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96595417706625</v>
+        <v>88.00871910706321</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92470992680119</v>
+        <v>45.88217038971462</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228576142588665</v>
+        <v>2.228718203275916</v>
       </c>
       <c r="E3" t="n">
-        <v>5.700624252823604</v>
+        <v>5.678910857887147</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428587141962218</v>
+        <v>0.7429060677586389</v>
       </c>
       <c r="G3" t="n">
-        <v>33.972404597964</v>
+        <v>33.95714335164673</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1715008530262</v>
+        <v>34.17367911689738</v>
       </c>
       <c r="I3" t="n">
-        <v>6.507122652741154</v>
+        <v>6.584198586105914</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642866963726386</v>
+        <v>4.643162923491493</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03404582293376</v>
+        <v>11.99128089293677</v>
       </c>
       <c r="L3" t="n">
-        <v>48.80765572606296</v>
+        <v>48.89020843614382</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7664114757979</v>
+        <v>106.7636597187952</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.9551715950835</v>
+        <v>87.15141565725878</v>
       </c>
       <c r="C4" t="n">
-        <v>42.53744816069266</v>
+        <v>42.66484705661203</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179346924126636</v>
+        <v>2.187669695335599</v>
       </c>
       <c r="E4" t="n">
-        <v>6.480347141780478</v>
+        <v>6.490711895040362</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444061085358175</v>
+        <v>0.7444683958447491</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22195461527194</v>
+        <v>33.33172104996151</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2426809926476</v>
+        <v>34.24554620885845</v>
       </c>
       <c r="I4" t="n">
-        <v>5.433897634372154</v>
+        <v>5.498370938188432</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652538178348859</v>
+        <v>4.652927474029682</v>
       </c>
       <c r="K4" t="n">
-        <v>13.04482840491653</v>
+        <v>12.8485843427412</v>
       </c>
       <c r="L4" t="n">
-        <v>44.23697002737021</v>
+        <v>44.30367419547714</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8192465929794</v>
+        <v>99.81710559483038</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.60719402766539</v>
+        <v>86.11873804668652</v>
       </c>
       <c r="C5" t="n">
-        <v>42.0327852270707</v>
+        <v>42.4855560559139</v>
       </c>
       <c r="D5" t="n">
-        <v>2.112929266247751</v>
+        <v>2.13768437275013</v>
       </c>
       <c r="E5" t="n">
-        <v>7.038893483566132</v>
+        <v>7.107427221867636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457209549817141</v>
+        <v>0.7457910644738333</v>
       </c>
       <c r="G5" t="n">
-        <v>32.20948414015965</v>
+        <v>32.57013586524943</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30316392915885</v>
+        <v>34.30638896579632</v>
       </c>
       <c r="I5" t="n">
-        <v>4.53624628491558</v>
+        <v>4.590116403587717</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660755968635713</v>
+        <v>4.661194152961458</v>
       </c>
       <c r="K5" t="n">
-        <v>14.39280597233462</v>
+        <v>13.88126195331348</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42346719963992</v>
+        <v>43.48044946471182</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84905839904523</v>
+        <v>99.8472674739392</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.06408670538505</v>
+        <v>84.88754829888488</v>
       </c>
       <c r="C6" t="n">
-        <v>41.19395472891318</v>
+        <v>41.96736494370435</v>
       </c>
       <c r="D6" t="n">
-        <v>2.037153684042849</v>
+        <v>2.077864339163915</v>
       </c>
       <c r="E6" t="n">
-        <v>7.417438985388335</v>
+        <v>7.547011229889069</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468404223574454</v>
+        <v>0.7469129465128579</v>
       </c>
       <c r="G6" t="n">
-        <v>31.05436150911461</v>
+        <v>31.65870729038443</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35465942844249</v>
+        <v>34.35799553959145</v>
       </c>
       <c r="I6" t="n">
-        <v>3.78588003630529</v>
+        <v>3.830851037637804</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667752639734034</v>
+        <v>4.668205915705362</v>
       </c>
       <c r="K6" t="n">
-        <v>15.93591329461495</v>
+        <v>15.11245170111511</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74412513522421</v>
+        <v>42.79268012174754</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87399315875234</v>
+        <v>99.87249676656701</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.27237169703074</v>
+        <v>83.48151404300273</v>
       </c>
       <c r="C7" t="n">
-        <v>39.989896264258</v>
+        <v>41.15652419418448</v>
       </c>
       <c r="D7" t="n">
-        <v>1.949542148058497</v>
+        <v>2.00965821528068</v>
       </c>
       <c r="E7" t="n">
-        <v>7.624928046246666</v>
+        <v>7.832021483290156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477962809122313</v>
+        <v>0.7478662394505073</v>
       </c>
       <c r="G7" t="n">
-        <v>29.7188116524011</v>
+        <v>30.61950676572464</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39862892196264</v>
+        <v>34.40184701472332</v>
       </c>
       <c r="I7" t="n">
-        <v>3.158937891748157</v>
+        <v>3.196450327967749</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673726755701446</v>
+        <v>4.674163996565671</v>
       </c>
       <c r="K7" t="n">
-        <v>17.72762830296926</v>
+        <v>16.51848595699727</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17731209843093</v>
+        <v>42.21857731999498</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8948366656582</v>
+        <v>99.89358747117673</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.23328372624171</v>
+        <v>88.20963184266768</v>
       </c>
       <c r="C8" t="n">
-        <v>42.36585042004985</v>
+        <v>43.41545219911449</v>
       </c>
       <c r="D8" t="n">
-        <v>1.953728923317374</v>
+        <v>2.013869460894406</v>
       </c>
       <c r="E8" t="n">
-        <v>9.506712118338111</v>
+        <v>9.630521491292775</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494022246312328</v>
+        <v>0.7494333956945853</v>
       </c>
       <c r="G8" t="n">
-        <v>30.24699071856401</v>
+        <v>31.11260507872905</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47250233303672</v>
+        <v>34.47393620195091</v>
       </c>
       <c r="I8" t="n">
-        <v>5.620183504409051</v>
+        <v>5.545307491014783</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683763903945206</v>
+        <v>4.683958723091159</v>
       </c>
       <c r="K8" t="n">
-        <v>12.76671627375829</v>
+        <v>11.79036815733231</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68049531817483</v>
+        <v>44.60972259089951</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81306201198298</v>
+        <v>99.81554294734632</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.89641367435718</v>
+        <v>86.10683598635008</v>
       </c>
       <c r="C9" t="n">
-        <v>40.90054497524526</v>
+        <v>42.17381516626747</v>
       </c>
       <c r="D9" t="n">
-        <v>1.847659031993298</v>
+        <v>1.918258609302095</v>
       </c>
       <c r="E9" t="n">
-        <v>9.772602337203621</v>
+        <v>9.944862852706994</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507828409072713</v>
+        <v>0.7507764579590088</v>
       </c>
       <c r="G9" t="n">
-        <v>28.60485143296095</v>
+        <v>29.63549709104874</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53601068173448</v>
+        <v>34.53571706611439</v>
       </c>
       <c r="I9" t="n">
-        <v>4.692114593887113</v>
+        <v>4.629371046975034</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692392755670446</v>
+        <v>4.692352862243806</v>
       </c>
       <c r="K9" t="n">
-        <v>15.1035863256428</v>
+        <v>13.89316401364993</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83975249065613</v>
+        <v>43.77898450088772</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8438837915442</v>
+        <v>99.84596368080513</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.41817237761958</v>
+        <v>83.84233161108888</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14933692881186</v>
+        <v>40.62785883672439</v>
       </c>
       <c r="D10" t="n">
-        <v>1.736572264901908</v>
+        <v>1.816368580260243</v>
       </c>
       <c r="E10" t="n">
-        <v>9.837759150964773</v>
+        <v>10.06058840151152</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519720132692064</v>
+        <v>0.7519297343511618</v>
       </c>
       <c r="G10" t="n">
-        <v>26.88504252136267</v>
+        <v>28.06138104400791</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59071261038349</v>
+        <v>34.58876778015343</v>
       </c>
       <c r="I10" t="n">
-        <v>3.916288733805008</v>
+        <v>3.863735231109844</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69982508293254</v>
+        <v>4.699560839694763</v>
       </c>
       <c r="K10" t="n">
-        <v>17.58182762238041</v>
+        <v>16.15766838891113</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13849893231085</v>
+        <v>43.08587913417073</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86966348350312</v>
+        <v>99.87140635980626</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.83619914181045</v>
+        <v>81.55560520827756</v>
       </c>
       <c r="C11" t="n">
-        <v>37.17330170549567</v>
+        <v>38.94017125052923</v>
       </c>
       <c r="D11" t="n">
-        <v>1.622197769780137</v>
+        <v>1.714626234223418</v>
       </c>
       <c r="E11" t="n">
-        <v>9.734493713420937</v>
+        <v>10.03439009278805</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529980577905031</v>
+        <v>0.752920566758826</v>
       </c>
       <c r="G11" t="n">
-        <v>25.1143340821824</v>
+        <v>26.48954657633528</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63791065836314</v>
+        <v>34.63434607090598</v>
       </c>
       <c r="I11" t="n">
-        <v>3.268026999082689</v>
+        <v>3.224022125023323</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706237861190644</v>
+        <v>4.705753542242664</v>
       </c>
       <c r="K11" t="n">
-        <v>20.16380085818956</v>
+        <v>18.44439479172244</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55411163815354</v>
+        <v>42.5081079791064</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89121420183876</v>
+        <v>99.89267402135808</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.31987926933931</v>
+        <v>79.161535152667</v>
       </c>
       <c r="C12" t="n">
-        <v>35.16159638946431</v>
+        <v>37.04519426519271</v>
       </c>
       <c r="D12" t="n">
-        <v>1.512049413139449</v>
+        <v>1.609095949833907</v>
       </c>
       <c r="E12" t="n">
-        <v>9.527940985337841</v>
+        <v>9.865090414583303</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538831652749899</v>
+        <v>0.7537733174202597</v>
       </c>
       <c r="G12" t="n">
-        <v>23.40905333355176</v>
+        <v>24.85919161747979</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67862560264953</v>
+        <v>34.67357260133193</v>
       </c>
       <c r="I12" t="n">
-        <v>2.726556986417034</v>
+        <v>2.689728018141185</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711769782968687</v>
+        <v>4.711083233876624</v>
       </c>
       <c r="K12" t="n">
-        <v>22.68012073066071</v>
+        <v>20.83846484733299</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06750435212269</v>
+        <v>42.02678471733475</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90922147224769</v>
+        <v>99.91044382986044</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.7457294513617</v>
+        <v>76.78570902742037</v>
       </c>
       <c r="C13" t="n">
-        <v>33.00746554966217</v>
+        <v>35.08489850992358</v>
       </c>
       <c r="D13" t="n">
-        <v>1.400483002795759</v>
+        <v>1.505342502662588</v>
       </c>
       <c r="E13" t="n">
-        <v>9.20399541390651</v>
+        <v>9.602933068644742</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546478281762466</v>
+        <v>0.7545074745381904</v>
       </c>
       <c r="G13" t="n">
-        <v>21.68181874235821</v>
+        <v>23.25628731306455</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71380009610734</v>
+        <v>34.70734382875675</v>
       </c>
       <c r="I13" t="n">
-        <v>2.27443544191609</v>
+        <v>2.243623123889858</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716548926101542</v>
+        <v>4.715671715863691</v>
       </c>
       <c r="K13" t="n">
-        <v>25.25427054863829</v>
+        <v>23.21429097257963</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66252620763242</v>
+        <v>41.62609585032621</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92426230593287</v>
+        <v>99.92528533282942</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.36339336705819</v>
+        <v>83.74167878652733</v>
       </c>
       <c r="C14" t="n">
-        <v>37.85022715582362</v>
+        <v>39.31626206567996</v>
       </c>
       <c r="D14" t="n">
-        <v>1.402082684823556</v>
+        <v>1.50717627333432</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85709237147576</v>
+        <v>11.97081349098026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555098140522908</v>
+        <v>0.7554265967153453</v>
       </c>
       <c r="G14" t="n">
-        <v>23.8787761755002</v>
+        <v>25.13073979398232</v>
       </c>
       <c r="H14" t="n">
-        <v>36.92564312680143</v>
+        <v>36.59574570096698</v>
       </c>
       <c r="I14" t="n">
-        <v>2.822352856578129</v>
+        <v>3.060360701077208</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721936337826818</v>
+        <v>4.721416229470909</v>
       </c>
       <c r="K14" t="n">
-        <v>17.63660663294182</v>
+        <v>16.25832121347268</v>
       </c>
       <c r="L14" t="n">
-        <v>44.41919511984044</v>
+        <v>44.32352881478271</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90602890860588</v>
+        <v>99.89811209393535</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.60474782860148</v>
+        <v>83.00593742201066</v>
       </c>
       <c r="C15" t="n">
-        <v>37.50152895631324</v>
+        <v>39.05346488786743</v>
       </c>
       <c r="D15" t="n">
-        <v>1.371896043543016</v>
+        <v>1.479970701499678</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01948557592695</v>
+        <v>12.18021790251095</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562363396563185</v>
+        <v>0.756201055367821</v>
       </c>
       <c r="G15" t="n">
-        <v>23.38997382584939</v>
+        <v>24.67711259800055</v>
       </c>
       <c r="H15" t="n">
-        <v>36.98645647634121</v>
+        <v>36.63326343204125</v>
       </c>
       <c r="I15" t="n">
-        <v>2.354222444432595</v>
+        <v>2.552915136541529</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726477122851991</v>
+        <v>4.726256596048882</v>
       </c>
       <c r="K15" t="n">
-        <v>18.39525217139855</v>
+        <v>16.99406257798933</v>
       </c>
       <c r="L15" t="n">
-        <v>44.02482018182771</v>
+        <v>43.8674625146689</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92160130953951</v>
+        <v>99.91498998052566</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.05208598783526</v>
+        <v>80.57752557069394</v>
       </c>
       <c r="C16" t="n">
-        <v>35.31190528371398</v>
+        <v>37.01966195280414</v>
       </c>
       <c r="D16" t="n">
-        <v>1.27774212356282</v>
+        <v>1.387445503960785</v>
       </c>
       <c r="E16" t="n">
-        <v>11.52182824669021</v>
+        <v>11.77361570772147</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568624467410054</v>
+        <v>0.7568671556387149</v>
       </c>
       <c r="G16" t="n">
-        <v>21.78470808118668</v>
+        <v>23.13434238268086</v>
       </c>
       <c r="H16" t="n">
-        <v>37.01707849385471</v>
+        <v>36.66553186981001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.963476303668525</v>
+        <v>2.129303228140129</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730390292131283</v>
+        <v>4.73041972274197</v>
       </c>
       <c r="K16" t="n">
-        <v>20.94791401216477</v>
+        <v>19.42247442930607</v>
       </c>
       <c r="L16" t="n">
-        <v>43.67478563622036</v>
+        <v>43.4869493085414</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93460493209912</v>
+        <v>99.92908569065162</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.1505717056628</v>
+        <v>82.24359069470894</v>
       </c>
       <c r="C17" t="n">
-        <v>36.82788469619786</v>
+        <v>38.22101854694404</v>
       </c>
       <c r="D17" t="n">
-        <v>1.278754961419156</v>
+        <v>1.388655421478711</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43573814606815</v>
+        <v>12.54806701835371</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574623948243957</v>
+        <v>0.757527179277651</v>
       </c>
       <c r="G17" t="n">
-        <v>22.38512184168357</v>
+        <v>23.56009944767124</v>
       </c>
       <c r="H17" t="n">
-        <v>37.62956661670624</v>
+        <v>37.10308876632682</v>
       </c>
       <c r="I17" t="n">
-        <v>1.929787777308822</v>
+        <v>2.151607991115477</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734139967652473</v>
+        <v>4.734544870485321</v>
       </c>
       <c r="K17" t="n">
-        <v>18.84942829433721</v>
+        <v>17.75640930529106</v>
       </c>
       <c r="L17" t="n">
-        <v>44.2584116998344</v>
+        <v>43.95091437033537</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93572469036945</v>
+        <v>99.92834222257048</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.6133134863762</v>
+        <v>79.97562587069726</v>
       </c>
       <c r="C18" t="n">
-        <v>34.58784520489046</v>
+        <v>36.28521868598011</v>
       </c>
       <c r="D18" t="n">
-        <v>1.189689013667712</v>
+        <v>1.305639448288566</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83779148795236</v>
+        <v>12.09698205873027</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579792492808078</v>
+        <v>0.7580937131689706</v>
       </c>
       <c r="G18" t="n">
-        <v>20.82598646976804</v>
+        <v>22.15164018999427</v>
       </c>
       <c r="H18" t="n">
-        <v>37.65524315105513</v>
+        <v>37.13083715322801</v>
       </c>
       <c r="I18" t="n">
-        <v>1.609253806647094</v>
+        <v>1.794347599981094</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737370308005048</v>
+        <v>4.738085707306068</v>
       </c>
       <c r="K18" t="n">
-        <v>21.38668651362379</v>
+        <v>20.02437412930275</v>
       </c>
       <c r="L18" t="n">
-        <v>43.9718630654494</v>
+        <v>43.63064029607504</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94639478396365</v>
+        <v>99.94023311135791</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.6494532253008</v>
+        <v>79.09687331810299</v>
       </c>
       <c r="C19" t="n">
-        <v>33.86442327521165</v>
+        <v>35.68281780202962</v>
       </c>
       <c r="D19" t="n">
-        <v>1.156213342703192</v>
+        <v>1.274172426571873</v>
       </c>
       <c r="E19" t="n">
-        <v>11.72941099747144</v>
+        <v>12.05480658394114</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584179594193252</v>
+        <v>0.7585717280464992</v>
       </c>
       <c r="G19" t="n">
-        <v>20.23998133517895</v>
+        <v>21.61776681183263</v>
       </c>
       <c r="H19" t="n">
-        <v>37.67703759589565</v>
+        <v>37.15424994806592</v>
       </c>
       <c r="I19" t="n">
-        <v>1.348279748261442</v>
+        <v>1.496232519354288</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740112246370782</v>
+        <v>4.741073300290622</v>
       </c>
       <c r="K19" t="n">
-        <v>22.35054677469923</v>
+        <v>20.90312668189703</v>
       </c>
       <c r="L19" t="n">
-        <v>43.74011328908818</v>
+        <v>43.36421252718499</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95508333899905</v>
+        <v>99.95015701111163</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.96265519570332</v>
+        <v>76.69265173021887</v>
       </c>
       <c r="C20" t="n">
-        <v>31.38448668132288</v>
+        <v>33.50890603464059</v>
       </c>
       <c r="D20" t="n">
-        <v>1.06296464071437</v>
+        <v>1.187156894644742</v>
       </c>
       <c r="E20" t="n">
-        <v>10.97078770837981</v>
+        <v>11.4394848630628</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587970632658304</v>
+        <v>0.7589830433875009</v>
       </c>
       <c r="G20" t="n">
-        <v>18.6076251617319</v>
+        <v>20.1414505464828</v>
       </c>
       <c r="H20" t="n">
-        <v>37.69587089183771</v>
+        <v>37.17439585177157</v>
       </c>
       <c r="I20" t="n">
-        <v>1.124128084362259</v>
+        <v>1.247536509697575</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74248164541144</v>
+        <v>4.743644021171882</v>
       </c>
       <c r="K20" t="n">
-        <v>25.03734480429668</v>
+        <v>23.30734826978112</v>
       </c>
       <c r="L20" t="n">
-        <v>43.54071629915097</v>
+        <v>43.14218368115178</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96254778477052</v>
+        <v>99.95843798557351</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.38492470014353</v>
+        <v>82.51654600892067</v>
       </c>
       <c r="C21" t="n">
-        <v>35.45282984229915</v>
+        <v>37.01968620060948</v>
       </c>
       <c r="D21" t="n">
-        <v>1.063637551821851</v>
+        <v>1.188082675475429</v>
       </c>
       <c r="E21" t="n">
-        <v>13.13414525602011</v>
+        <v>13.35694520943648</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759277420704486</v>
+        <v>0.7595749213065484</v>
       </c>
       <c r="G21" t="n">
-        <v>20.518213072433</v>
+        <v>21.74395246468594</v>
       </c>
       <c r="H21" t="n">
-        <v>39.61854264059149</v>
+        <v>38.79018057557937</v>
       </c>
       <c r="I21" t="n">
-        <v>1.545624879169558</v>
+        <v>1.930466904270971</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745483879403037</v>
+        <v>4.747343258165929</v>
       </c>
       <c r="K21" t="n">
-        <v>18.61507529985645</v>
+        <v>17.48345399107933</v>
       </c>
       <c r="L21" t="n">
-        <v>45.88060662323066</v>
+        <v>45.43256105361463</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94851176538627</v>
+        <v>99.93570124530345</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_19_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.72753214021292</v>
+        <v>43.27782371049431</v>
       </c>
       <c r="M2" t="n">
-        <v>99.28854918372429</v>
+        <v>96.88022552896842</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00871910706321</v>
+        <v>81.44875362209916</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88217038971462</v>
+        <v>43.20430917765474</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228718203275916</v>
+        <v>2.178786615903396</v>
       </c>
       <c r="E3" t="n">
-        <v>5.678910857887147</v>
+        <v>4.146099137335764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429060677586389</v>
+        <v>0.7376131063218536</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95714335164673</v>
+        <v>32.77258201421358</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17367911689738</v>
+        <v>33.93020289080526</v>
       </c>
       <c r="I3" t="n">
-        <v>6.584198586105914</v>
+        <v>3.073387943007723</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643162923491493</v>
+        <v>4.610081914511585</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99128089293677</v>
+        <v>18.55124637790082</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89020843614382</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636597187952</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15141565725878</v>
+        <v>88.38098242990711</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66484705661203</v>
+        <v>42.70775550487804</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187669695335599</v>
+        <v>2.184473770259272</v>
       </c>
       <c r="E4" t="n">
-        <v>6.490711895040362</v>
+        <v>6.46152929727288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444683958447491</v>
+        <v>0.7395384530079175</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33172104996151</v>
+        <v>33.43369144430419</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24554620885845</v>
+        <v>34.0187688383642</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498370938188432</v>
+        <v>6.920865295399158</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652927474029682</v>
+        <v>4.622115331299485</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8485843427412</v>
+        <v>11.61901757009291</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30367419547714</v>
+        <v>45.44313201794154</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81710559483038</v>
+        <v>99.7699050929125</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.11873804668652</v>
+        <v>87.15096866776651</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4855560559139</v>
+        <v>42.55045049373132</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13768437275013</v>
+        <v>2.125308557508837</v>
       </c>
       <c r="E5" t="n">
-        <v>7.107427221867636</v>
+        <v>7.249878859348196</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457910644738333</v>
+        <v>0.7411734068854625</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57013586524943</v>
+        <v>32.52815918556717</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30638896579632</v>
+        <v>34.09397671673128</v>
       </c>
       <c r="I5" t="n">
-        <v>4.590116403587717</v>
+        <v>5.780138148691415</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661194152961458</v>
+        <v>4.632333793034141</v>
       </c>
       <c r="K5" t="n">
-        <v>13.88126195331348</v>
+        <v>12.84903133223351</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48044946471182</v>
+        <v>44.40827191582965</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8472674739392</v>
+        <v>99.80775374179449</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.88754829888488</v>
+        <v>85.57581396346467</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96736494370435</v>
+        <v>41.87216227010391</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077864339163915</v>
+        <v>2.049262683628259</v>
       </c>
       <c r="E6" t="n">
-        <v>7.547011229889069</v>
+        <v>7.794776256371113</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469129465128579</v>
+        <v>0.7425666281891974</v>
       </c>
       <c r="G6" t="n">
-        <v>31.65870729038443</v>
+        <v>31.36426593239528</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35799553959145</v>
+        <v>34.15806489670308</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830851037637804</v>
+        <v>4.825836139995262</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668205915705362</v>
+        <v>4.641041426182483</v>
       </c>
       <c r="K6" t="n">
-        <v>15.11245170111511</v>
+        <v>14.4241860365353</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79268012174754</v>
+        <v>43.5430923003416</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87249676656701</v>
+        <v>99.83944060698082</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.48151404300273</v>
+        <v>83.92240656614612</v>
       </c>
       <c r="C7" t="n">
-        <v>41.15652419418448</v>
+        <v>40.96771912270906</v>
       </c>
       <c r="D7" t="n">
-        <v>2.00965821528068</v>
+        <v>1.970186810039446</v>
       </c>
       <c r="E7" t="n">
-        <v>7.832021483290156</v>
+        <v>8.16532286314494</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478662394505073</v>
+        <v>0.7437546429353409</v>
       </c>
       <c r="G7" t="n">
-        <v>30.61950676572464</v>
+        <v>30.15399808928752</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40184701472332</v>
+        <v>34.21271357502568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196450327967749</v>
+        <v>4.027964067367326</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674163996565671</v>
+        <v>4.64846651834588</v>
       </c>
       <c r="K7" t="n">
-        <v>16.51848595699727</v>
+        <v>16.07759343385388</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21857731999498</v>
+        <v>42.82063643954828</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89358747117673</v>
+        <v>99.86594899611121</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.20963184266768</v>
+        <v>82.08361043083796</v>
       </c>
       <c r="C8" t="n">
-        <v>43.41545219911449</v>
+        <v>39.7539057239001</v>
       </c>
       <c r="D8" t="n">
-        <v>2.013869460894406</v>
+        <v>1.88283480101786</v>
       </c>
       <c r="E8" t="n">
-        <v>9.630521491292775</v>
+        <v>8.363500685986157</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494333956945853</v>
+        <v>0.7447698361710381</v>
       </c>
       <c r="G8" t="n">
-        <v>31.11260507872905</v>
+        <v>28.81706277954418</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47393620195091</v>
+        <v>34.25941246386775</v>
       </c>
       <c r="I8" t="n">
-        <v>5.545307491014783</v>
+        <v>3.361218388181983</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683958723091159</v>
+        <v>4.654811476068987</v>
       </c>
       <c r="K8" t="n">
-        <v>11.79036815733231</v>
+        <v>17.91638956916204</v>
       </c>
       <c r="L8" t="n">
-        <v>44.60972259089951</v>
+        <v>42.21781681617767</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81554294734632</v>
+        <v>99.8881121092398</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.10683598635008</v>
+        <v>80.07313110012667</v>
       </c>
       <c r="C9" t="n">
-        <v>42.17381516626747</v>
+        <v>38.26452465925544</v>
       </c>
       <c r="D9" t="n">
-        <v>1.918258609302095</v>
+        <v>1.788015646668879</v>
       </c>
       <c r="E9" t="n">
-        <v>9.944862852706994</v>
+        <v>8.409697460367742</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507764579590088</v>
+        <v>0.7456392693131521</v>
       </c>
       <c r="G9" t="n">
-        <v>29.63549709104874</v>
+        <v>27.36584171538031</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53571706611439</v>
+        <v>34.299406388405</v>
       </c>
       <c r="I9" t="n">
-        <v>4.629371046975034</v>
+        <v>2.804285186784401</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692352862243806</v>
+        <v>4.6602454332072</v>
       </c>
       <c r="K9" t="n">
-        <v>13.89316401364993</v>
+        <v>19.92686889987333</v>
       </c>
       <c r="L9" t="n">
-        <v>43.77898450088772</v>
+        <v>41.71523926342172</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84596368080513</v>
+        <v>99.90663282255049</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.84233161108888</v>
+        <v>85.17035731565542</v>
       </c>
       <c r="C10" t="n">
-        <v>40.62785883672439</v>
+        <v>41.81233484555249</v>
       </c>
       <c r="D10" t="n">
-        <v>1.816368580260243</v>
+        <v>1.789967436142587</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06058840151152</v>
+        <v>10.40478873354031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519297343511618</v>
+        <v>0.7464532056339781</v>
       </c>
       <c r="G10" t="n">
-        <v>28.06138104400791</v>
+        <v>28.91676761837608</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58876778015343</v>
+        <v>35.8579009380003</v>
       </c>
       <c r="I10" t="n">
-        <v>3.863735231109844</v>
+        <v>2.789146848749814</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699560839694763</v>
+        <v>4.665332535212363</v>
       </c>
       <c r="K10" t="n">
-        <v>16.15766838891113</v>
+        <v>14.82964268434456</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08587913417073</v>
+        <v>43.26515228513526</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87140635980626</v>
+        <v>99.90712981503231</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.55560520827756</v>
+        <v>84.78047584986791</v>
       </c>
       <c r="C11" t="n">
-        <v>38.94017125052923</v>
+        <v>41.7423791537316</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714626234223418</v>
+        <v>1.766796823207569</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03439009278805</v>
+        <v>10.69865055702096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752920566758826</v>
+        <v>0.7471605141926355</v>
       </c>
       <c r="G11" t="n">
-        <v>26.48954657633528</v>
+        <v>28.56932463226311</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63434607090598</v>
+        <v>35.91875466225891</v>
       </c>
       <c r="I11" t="n">
-        <v>3.224022125023323</v>
+        <v>2.410035447220758</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705753542242664</v>
+        <v>4.669753213703971</v>
       </c>
       <c r="K11" t="n">
-        <v>18.44439479172244</v>
+        <v>15.2195241501321</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5081079791064</v>
+        <v>42.95783823087137</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89267402135808</v>
+        <v>99.91974153473507</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.161535152667</v>
+        <v>82.72557973010889</v>
       </c>
       <c r="C12" t="n">
-        <v>37.04519426519271</v>
+        <v>40.0617635523726</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609095949833907</v>
+        <v>1.67968030790831</v>
       </c>
       <c r="E12" t="n">
-        <v>9.865090414583303</v>
+        <v>10.5061239908011</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537733174202597</v>
+        <v>0.7477656413114694</v>
       </c>
       <c r="G12" t="n">
-        <v>24.85919161747979</v>
+        <v>27.16063973215243</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67357260133193</v>
+        <v>35.94784534907653</v>
       </c>
       <c r="I12" t="n">
-        <v>2.689728018141185</v>
+        <v>2.009989450662371</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711083233876624</v>
+        <v>4.673535258196683</v>
       </c>
       <c r="K12" t="n">
-        <v>20.83846484733299</v>
+        <v>17.27442026989109</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02678471733475</v>
+        <v>42.59687074864684</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91044382986044</v>
+        <v>99.93305457091054</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.78570902742037</v>
+        <v>83.91526159811522</v>
       </c>
       <c r="C13" t="n">
-        <v>35.08489850992358</v>
+        <v>41.05981532283283</v>
       </c>
       <c r="D13" t="n">
-        <v>1.505342502662588</v>
+        <v>1.680911172516087</v>
       </c>
       <c r="E13" t="n">
-        <v>9.602933068644742</v>
+        <v>11.15071158773263</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545074745381904</v>
+        <v>0.7483136016932566</v>
       </c>
       <c r="G13" t="n">
-        <v>23.25628731306455</v>
+        <v>27.50996746835551</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70734382875675</v>
+        <v>36.30361232276081</v>
       </c>
       <c r="I13" t="n">
-        <v>2.243623123889858</v>
+        <v>1.844785434474066</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715671715863691</v>
+        <v>4.676960010582853</v>
       </c>
       <c r="K13" t="n">
-        <v>23.21429097257963</v>
+        <v>16.08473840188481</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62609585032621</v>
+        <v>42.79399845624097</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92528533282942</v>
+        <v>99.9385521809586</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.74167878652733</v>
+        <v>81.83573342845666</v>
       </c>
       <c r="C14" t="n">
-        <v>39.31626206567996</v>
+        <v>39.26659585987144</v>
       </c>
       <c r="D14" t="n">
-        <v>1.50717627333432</v>
+        <v>1.595262492741237</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97081349098026</v>
+        <v>10.83892207496766</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554265967153453</v>
+        <v>0.7487824755874327</v>
       </c>
       <c r="G14" t="n">
-        <v>25.13073979398232</v>
+        <v>26.10823224710237</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59574570096698</v>
+        <v>36.32635922465317</v>
       </c>
       <c r="I14" t="n">
-        <v>3.060360701077208</v>
+        <v>1.53828444098334</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721416229470909</v>
+        <v>4.679890472421454</v>
       </c>
       <c r="K14" t="n">
-        <v>16.25832121347268</v>
+        <v>18.16426657154336</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32352881478271</v>
+        <v>42.51789352873872</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89811209393535</v>
+        <v>99.94875596015351</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.00593742201066</v>
+        <v>80.92281605575455</v>
       </c>
       <c r="C15" t="n">
-        <v>39.05346488786743</v>
+        <v>38.55656125554664</v>
       </c>
       <c r="D15" t="n">
-        <v>1.479970701499678</v>
+        <v>1.556620794509594</v>
       </c>
       <c r="E15" t="n">
-        <v>12.18021790251095</v>
+        <v>10.79584785730828</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756201055367821</v>
+        <v>0.7491886373533384</v>
       </c>
       <c r="G15" t="n">
-        <v>24.67711259800055</v>
+        <v>25.47581818581482</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63326343204125</v>
+        <v>36.34606371653519</v>
       </c>
       <c r="I15" t="n">
-        <v>2.552915136541529</v>
+        <v>1.316847880774979</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726256596048882</v>
+        <v>4.682428983458365</v>
       </c>
       <c r="K15" t="n">
-        <v>16.99406257798933</v>
+        <v>19.07718394424543</v>
       </c>
       <c r="L15" t="n">
-        <v>43.8674625146689</v>
+        <v>42.32238366784882</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91498998052566</v>
+        <v>99.9561288676409</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.57752557069394</v>
+        <v>78.59377670706168</v>
       </c>
       <c r="C16" t="n">
-        <v>37.01966195280414</v>
+        <v>36.43133166528967</v>
       </c>
       <c r="D16" t="n">
-        <v>1.387445503960785</v>
+        <v>1.461461831985099</v>
       </c>
       <c r="E16" t="n">
-        <v>11.77361570772147</v>
+        <v>10.31885942262433</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568671556387149</v>
+        <v>0.7495374870165809</v>
       </c>
       <c r="G16" t="n">
-        <v>23.13434238268086</v>
+        <v>23.91843668572471</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66553186981001</v>
+        <v>36.36298777471698</v>
       </c>
       <c r="I16" t="n">
-        <v>2.129303228140129</v>
+        <v>1.097884211140358</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73041972274197</v>
+        <v>4.68460929385363</v>
       </c>
       <c r="K16" t="n">
-        <v>19.42247442930607</v>
+        <v>21.4062232929383</v>
       </c>
       <c r="L16" t="n">
-        <v>43.4869493085414</v>
+        <v>42.1258659339727</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92908569065162</v>
+        <v>99.96342089220067</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.24359069470894</v>
+        <v>83.52285704072774</v>
       </c>
       <c r="C17" t="n">
-        <v>38.22101854694404</v>
+        <v>39.73669013431613</v>
       </c>
       <c r="D17" t="n">
-        <v>1.388655421478711</v>
+        <v>1.462134037623178</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54806701835371</v>
+        <v>12.06460097623159</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757527179277651</v>
+        <v>0.7498822399986271</v>
       </c>
       <c r="G17" t="n">
-        <v>23.56009944767124</v>
+        <v>25.4783499415274</v>
       </c>
       <c r="H17" t="n">
-        <v>37.10308876632682</v>
+        <v>37.92862495516983</v>
       </c>
       <c r="I17" t="n">
-        <v>2.151607991115477</v>
+        <v>1.152500890185713</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734544870485321</v>
+        <v>4.686763999991419</v>
       </c>
       <c r="K17" t="n">
-        <v>17.75640930529106</v>
+        <v>16.47714295927226</v>
       </c>
       <c r="L17" t="n">
-        <v>43.95091437033537</v>
+        <v>43.74776787187272</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92834222257048</v>
+        <v>99.9616009654611</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.97562587069726</v>
+        <v>85.2357220778042</v>
       </c>
       <c r="C18" t="n">
-        <v>36.28521868598011</v>
+        <v>40.46278632805414</v>
       </c>
       <c r="D18" t="n">
-        <v>1.305639448288566</v>
+        <v>1.463328902611969</v>
       </c>
       <c r="E18" t="n">
-        <v>12.09698205873027</v>
+        <v>12.66281722049314</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580937131689706</v>
+        <v>0.7504950484082772</v>
       </c>
       <c r="G18" t="n">
-        <v>22.15164018999427</v>
+        <v>25.61921159606564</v>
       </c>
       <c r="H18" t="n">
-        <v>37.13083715322801</v>
+        <v>37.95962046232977</v>
       </c>
       <c r="I18" t="n">
-        <v>1.794347599981094</v>
+        <v>2.089654795343673</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738085707306068</v>
+        <v>4.690594052551732</v>
       </c>
       <c r="K18" t="n">
-        <v>20.02437412930275</v>
+        <v>14.7642779221958</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63064029607504</v>
+        <v>44.70333746605365</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94023311135791</v>
+        <v>99.93040171630359</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.09687331810299</v>
+        <v>82.60459896051458</v>
       </c>
       <c r="C19" t="n">
-        <v>35.68281780202962</v>
+        <v>38.15495948297603</v>
       </c>
       <c r="D19" t="n">
-        <v>1.274172426571873</v>
+        <v>1.36741812954765</v>
       </c>
       <c r="E19" t="n">
-        <v>12.05480658394114</v>
+        <v>12.12329378284912</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585717280464992</v>
+        <v>0.7510227895299387</v>
       </c>
       <c r="G19" t="n">
-        <v>21.61776681183263</v>
+        <v>23.94005499286378</v>
       </c>
       <c r="H19" t="n">
-        <v>37.15424994806592</v>
+        <v>37.98631331356593</v>
       </c>
       <c r="I19" t="n">
-        <v>1.496232519354288</v>
+        <v>1.742603517596051</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741073300290622</v>
+        <v>4.693892434562116</v>
       </c>
       <c r="K19" t="n">
-        <v>20.90312668189703</v>
+        <v>17.39540103948542</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36421252718499</v>
+        <v>44.39159351100123</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95015701111163</v>
+        <v>99.94195403346268</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.69265173021887</v>
+        <v>79.91688790555217</v>
       </c>
       <c r="C20" t="n">
-        <v>33.50890603464059</v>
+        <v>35.73610690616086</v>
       </c>
       <c r="D20" t="n">
-        <v>1.187156894644742</v>
+        <v>1.270000098326143</v>
       </c>
       <c r="E20" t="n">
-        <v>11.4394848630628</v>
+        <v>11.50177723686642</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589830433875009</v>
+        <v>0.7514779596761603</v>
       </c>
       <c r="G20" t="n">
-        <v>20.1414505464828</v>
+        <v>22.23451008721674</v>
       </c>
       <c r="H20" t="n">
-        <v>37.17439585177157</v>
+        <v>38.0093355653889</v>
       </c>
       <c r="I20" t="n">
-        <v>1.247536509697575</v>
+        <v>1.453049710101792</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743644021171882</v>
+        <v>4.696737247976</v>
       </c>
       <c r="K20" t="n">
-        <v>23.30734826978112</v>
+        <v>20.08311209444783</v>
       </c>
       <c r="L20" t="n">
-        <v>43.14218368115178</v>
+        <v>44.13237534612475</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95843798557351</v>
+        <v>99.95159434673346</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.51654600892067</v>
+        <v>77.15325830062035</v>
       </c>
       <c r="C21" t="n">
-        <v>37.01968620060948</v>
+        <v>33.19594823689</v>
       </c>
       <c r="D21" t="n">
-        <v>1.188082675475429</v>
+        <v>1.170350092588828</v>
       </c>
       <c r="E21" t="n">
-        <v>13.35694520943648</v>
+        <v>10.80121337754345</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595749213065484</v>
+        <v>0.751871298854749</v>
       </c>
       <c r="G21" t="n">
-        <v>21.74395246468594</v>
+        <v>20.48988891696818</v>
       </c>
       <c r="H21" t="n">
-        <v>38.79018057557937</v>
+        <v>38.02923044139623</v>
       </c>
       <c r="I21" t="n">
-        <v>1.930466904270971</v>
+        <v>1.211508555426731</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747343258165929</v>
+        <v>4.69919561784218</v>
       </c>
       <c r="K21" t="n">
-        <v>17.48345399107933</v>
+        <v>22.84674169937965</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43256105361463</v>
+        <v>43.91694757178306</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93570124530345</v>
+        <v>99.95963750805272</v>
       </c>
     </row>
   </sheetData>
